--- a/Art_Courses.xlsx
+++ b/Art_Courses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\Spectrum Works Projects\photoshop-courses\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CJ\Documents\My Projects\Spectrum Works Projects\art-courses\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF152F2-9F66-4BAD-912E-F41CBA05BEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF6AA68-05E5-41C5-9D0F-D6B3732EDA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Photoshop" sheetId="1" r:id="rId1"/>
@@ -499,16 +499,10 @@
     <t>Basics of Animation</t>
   </si>
   <si>
-    <t>https://www.udemy.com/course/begin-animation/?utm_campaign=Search_DSA_Beta_Prof_la.EN_cc.US&amp;utm_source=google&amp;utm_medium=paid-search&amp;portfolio=USA&amp;utm_audience=mx&amp;utm_tactic=nb&amp;utm_term=_._ag_162107351473_._ad_696074114859_._kw_&amp;utm_content=g&amp;funnel=&amp;test=&amp;campaignid=21164973268&amp;adgroupid=162107351473&amp;device=c&amp;keyword=&amp;matchtype=&amp;network=g&amp;devicemodel=&amp;creativeid=696074114859&amp;assetgroupid=&amp;targetid=aud-1748515510702%3Adsa-2435203043973&amp;extensionid=&amp;placement=&amp;gad_source=1&amp;gad_campaignid=21164973268&amp;gbraid=0AAAAADROdO3vV3srGaLnx8wKT1ORyb2GY&amp;gclid=Cj0KCQjwnbrUBhDOARIsAKKhPpdRt5LScRL_ACtHKBxygXyQvQ412VeQAYV3I2zhz1xdaxIBluI9rSgaAst-EALw_wcB&amp;couponCode=CP260817G1</t>
-  </si>
-  <si>
     <t>This course is perfect if you want to pursue a career in animation and you have never animated before.</t>
   </si>
   <si>
     <t>$13/month</t>
-  </si>
-  <si>
-    <t>https://www.udemy.com/course/learn-animation/?couponCode=CP260817G1</t>
   </si>
   <si>
     <t>Learn How to Animate: 2D Animation for Beginners</t>
@@ -621,6 +615,12 @@
   </si>
   <si>
     <t>https://www.nobledesktop.com/seminars/intro-after-effects</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/begin-animation</t>
+  </si>
+  <si>
+    <t>https://www.udemy.com/course/learn-animation</t>
   </si>
 </sst>
 </file>
@@ -830,40 +830,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1226,6 +1199,33 @@
         <top/>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1268,56 +1268,56 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29CE4B51-B891-4FED-B6CE-0832EE7B1EAC}" name="Table1" displayName="Table1" ref="A1:H27" totalsRowShown="0" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{29CE4B51-B891-4FED-B6CE-0832EE7B1EAC}" name="Table1" displayName="Table1" ref="A1:H27" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A1:H27" xr:uid="{29CE4B51-B891-4FED-B6CE-0832EE7B1EAC}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{3DBB28DD-33B7-4042-B7F3-B5060E89F664}" name="ID" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{3DBB28DD-33B7-4042-B7F3-B5060E89F664}" name="ID" dataDxfId="19">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1F2E0A47-3518-43B8-ACAD-F8AA9B3FA0C2}" name="Course" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{08E04412-D137-43F6-90C3-6274D8F1475F}" name="Provider" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{EA2CEA01-9D57-4566-BB51-937CB5EF4C8B}" name="Link" dataDxfId="25"/>
-    <tableColumn id="6" xr3:uid="{44826D80-7922-4F2C-A047-A6EBCDA411EA}" name="Description" dataDxfId="24"/>
-    <tableColumn id="7" xr3:uid="{2D68A384-0B4A-4939-A697-890425BBF268}" name="Hours" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{F8C7365D-FC52-4C24-B91E-8694A3EEBDDB}" name="Cost" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{0D93BA61-F758-4D55-AE78-A86CE5502B5E}" name="Level" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{1F2E0A47-3518-43B8-ACAD-F8AA9B3FA0C2}" name="Course" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{08E04412-D137-43F6-90C3-6274D8F1475F}" name="Provider" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{EA2CEA01-9D57-4566-BB51-937CB5EF4C8B}" name="Link" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{44826D80-7922-4F2C-A047-A6EBCDA411EA}" name="Description" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{2D68A384-0B4A-4939-A697-890425BBF268}" name="Hours" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{F8C7365D-FC52-4C24-B91E-8694A3EEBDDB}" name="Cost" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{0D93BA61-F758-4D55-AE78-A86CE5502B5E}" name="Level" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C303FFE5-8D98-417D-880E-DB85C92CB383}" name="Table14" displayName="Table14" ref="A1:H16" totalsRowShown="0" dataDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C303FFE5-8D98-417D-880E-DB85C92CB383}" name="Table14" displayName="Table14" ref="A1:H16" totalsRowShown="0" dataDxfId="29">
   <autoFilter ref="A1:H16" xr:uid="{29CE4B51-B891-4FED-B6CE-0832EE7B1EAC}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{0227205A-05FB-49D8-9DB7-06580FAEFD61}" name="ID" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{0227205A-05FB-49D8-9DB7-06580FAEFD61}" name="ID" dataDxfId="28">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{30135BFE-F58A-462A-8C45-82F4C336217D}" name="Course" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{96FBC0EA-9DF0-4D17-A7EB-7E4095E2DFE5}" name="Provider" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{C01A10B6-88E6-4569-A16A-EDA93A283455}" name="Link" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{5FC3D772-8E9C-45C6-80F7-9A3456D7BE62}" name="Description" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{A9D41824-33F8-4A21-A318-1A7CEED0E54C}" name="Hours" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{7D5F93A2-6D53-45E3-99F7-AEC388991D3B}" name="Cost" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{964EDD01-5F45-4432-804F-4380823DEAD0}" name="Level" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{30135BFE-F58A-462A-8C45-82F4C336217D}" name="Course" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{96FBC0EA-9DF0-4D17-A7EB-7E4095E2DFE5}" name="Provider" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{C01A10B6-88E6-4569-A16A-EDA93A283455}" name="Link" dataDxfId="25"/>
+    <tableColumn id="6" xr3:uid="{5FC3D772-8E9C-45C6-80F7-9A3456D7BE62}" name="Description" dataDxfId="24"/>
+    <tableColumn id="7" xr3:uid="{A9D41824-33F8-4A21-A318-1A7CEED0E54C}" name="Hours" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{7D5F93A2-6D53-45E3-99F7-AEC388991D3B}" name="Cost" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{964EDD01-5F45-4432-804F-4380823DEAD0}" name="Level" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{99710536-DB71-4E03-8400-B3BDA29FD654}" name="Table2" displayName="Table2" ref="A1:G9" totalsRowShown="0" headerRowDxfId="20" dataDxfId="18" headerRowBorderDxfId="19" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{99710536-DB71-4E03-8400-B3BDA29FD654}" name="Table2" displayName="Table2" ref="A1:G9" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:G9" xr:uid="{99710536-DB71-4E03-8400-B3BDA29FD654}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{E134F453-3806-43C4-8FDF-00389ABDC66E}" name="ID" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{E134F453-3806-43C4-8FDF-00389ABDC66E}" name="ID" dataDxfId="6">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F5C13FF2-C72D-4500-AB55-A3687C29C9CB}" name="Course" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{5F865AA1-F175-4BE3-9CC1-280847A1B94F}" name="Link" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{7F5E2FFB-0415-4D23-A91F-D18147C0C87B}" name="Description" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{03D122FD-861D-4616-BC54-F434977F7341}" name="Hours" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{583253DF-20DD-4C32-A034-0A223219C6AA}" name="Cost" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{3B19AF21-D796-4E6D-B368-920BCCFDE861}" name="Level" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{F5C13FF2-C72D-4500-AB55-A3687C29C9CB}" name="Course" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{5F865AA1-F175-4BE3-9CC1-280847A1B94F}" name="Link" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{7F5E2FFB-0415-4D23-A91F-D18147C0C87B}" name="Description" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{03D122FD-861D-4616-BC54-F434977F7341}" name="Hours" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{583253DF-20DD-4C32-A034-0A223219C6AA}" name="Cost" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{3B19AF21-D796-4E6D-B368-920BCCFDE861}" name="Level" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2234,21 +2234,20 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="A26">
         <f>ROW()-1</f>
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="17" t="s">
+      <c r="B26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17">
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26">
         <v>80</v>
       </c>
       <c r="G26" t="s">
@@ -2259,26 +2258,25 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17">
+      <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H27" s="17" t="s">
+      <c r="G27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2356,367 +2354,361 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="17">
-        <f>ROW()-1</f>
+      <c r="A3">
+        <f t="shared" ref="A3:A16" si="1">ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" t="s">
         <v>112</v>
       </c>
-      <c r="F3" s="17">
+      <c r="F3">
         <v>2.25</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="17" t="s">
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
-        <f>ROW()-1</f>
+      <c r="A4">
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" t="s">
         <v>98</v>
       </c>
       <c r="D4" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4">
+        <v>4.5</v>
+      </c>
+      <c r="G4" t="s">
         <v>116</v>
       </c>
-      <c r="F4" s="17">
-        <v>4.5</v>
-      </c>
-      <c r="G4" s="17" t="s">
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17">
-        <f>ROW()-1</f>
-        <v>4</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="C5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5">
+        <v>1.5</v>
+      </c>
+      <c r="G5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="17">
-        <v>1.5</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
-        <f>ROW()-1</f>
-        <v>5</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="17">
+      <c r="F6">
         <v>80</v>
       </c>
       <c r="G6" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
-        <f>ROW()-1</f>
-        <v>6</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="A7">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" t="s">
         <v>126</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="F7">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="C8" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17">
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9">
         <v>0.5</v>
       </c>
-      <c r="G7" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H7" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
-        <f>ROW()-1</f>
-        <v>7</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17">
+      <c r="G9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10">
         <v>1</v>
       </c>
-      <c r="G8" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
-        <f>ROW()-1</f>
-        <v>8</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17">
-        <v>0.5</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
-        <f>ROW()-1</f>
-        <v>9</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="C11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
         <v>140</v>
       </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17">
+      <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13">
         <v>1</v>
       </c>
-      <c r="G10" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <f>ROW()-1</f>
-        <v>10</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17">
-        <v>6</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
-        <f>ROW()-1</f>
-        <v>11</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17">
-        <v>2</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
-        <f>ROW()-1</f>
-        <v>12</v>
-      </c>
-      <c r="B13" s="17" t="s">
+      <c r="G13" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>145</v>
       </c>
-      <c r="C13" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="C14" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17">
+      <c r="D14" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="G13" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <f>ROW()-1</f>
-        <v>13</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="G14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D15" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17">
+      <c r="F15">
         <v>1</v>
       </c>
-      <c r="G14" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="17">
-        <f>ROW()-1</f>
-        <v>14</v>
-      </c>
-      <c r="B15" s="17" t="s">
+      <c r="G15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17">
+      <c r="D16" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16">
         <v>1</v>
       </c>
-      <c r="G15" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
-        <f>ROW()-1</f>
-        <v>15</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17">
-        <v>1</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="17" t="s">
+      <c r="G16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{D7D1D8DA-96F6-4BC7-A302-42593A71E1E3}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{4EA0DE51-5F5D-4F6E-9FA3-B15CE77D2C7D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
